--- a/data/trans_orig/P36BPD14_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD14_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces a la semana que consume los vegetales cocinados, la pasta, el arroz u otros platos aderezados con una salsa de tomate, ajo, cebolla o puerro elaborada a fuego lento con aceite de oliva (sofrito) en 2023</t>
+          <t>Población según el número de veces a la semana que consume los vegetales cocinados, la pasta, el arroz u otros platos aderezados con una salsa de tomate, ajo, cebolla o puerro elaborada a fuego lento con aceite de oliva (sofrito) en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44712</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72009</t>
+          <t>70459</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65678</t>
+          <t>65927</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89953</t>
+          <t>88410</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>117695</t>
+          <t>116934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153785</t>
+          <t>149822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>212707</t>
+          <t>213185</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>252718</t>
+          <t>254969</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>361597</t>
+          <t>363092</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>404941</t>
+          <t>406359</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>587824</t>
+          <t>587029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>648691</t>
+          <t>646760</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,18%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>201295</t>
+          <t>199938</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>238508</t>
+          <t>242573</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>271736</t>
+          <t>271768</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>315317</t>
+          <t>313547</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>483375</t>
+          <t>484750</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>544422</t>
+          <t>542875</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>114110</t>
+          <t>116024</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>213961</t>
+          <t>213276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>129957</t>
+          <t>134813</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>217922</t>
+          <t>218374</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>279213</t>
+          <t>279290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>410004</t>
+          <t>410558</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>596947</t>
+          <t>618243</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1007803</t>
+          <t>1017365</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>587486</t>
+          <t>588762</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>961249</t>
+          <t>969756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1344555</t>
+          <t>1416083</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1917563</t>
+          <t>1938716</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,97%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1080862</t>
+          <t>1076106</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1583756</t>
+          <t>1567324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1060548</t>
+          <t>1052518</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1524449</t>
+          <t>1510838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2205678</t>
+          <t>2176152</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2893461</t>
+          <t>2802956</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>62,13%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43975</t>
+          <t>43455</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91657</t>
+          <t>89220</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59558</t>
+          <t>59076</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>89096</t>
+          <t>86303</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>109118</t>
+          <t>110661</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>163214</t>
+          <t>162131</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>224786</t>
+          <t>221988</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>275173</t>
+          <t>277916</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202881</t>
+          <t>203228</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>245281</t>
+          <t>247904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>439344</t>
+          <t>438415</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>506273</t>
+          <t>511078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>307245</t>
+          <t>305939</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>362191</t>
+          <t>365064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>341239</t>
+          <t>341960</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386360</t>
+          <t>386989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>662823</t>
+          <t>659762</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>734256</t>
+          <t>736355</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>224086</t>
+          <t>228834</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>335652</t>
+          <t>336842</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>274874</t>
+          <t>274702</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>374062</t>
+          <t>372062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>532742</t>
+          <t>537739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>682749</t>
+          <t>689951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1086953</t>
+          <t>1086852</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1502588</t>
+          <t>1507509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1172555</t>
+          <t>1144012</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1566737</t>
+          <t>1579608</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2443270</t>
+          <t>2456077</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3019323</t>
+          <t>3008180</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,49%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1623099</t>
+          <t>1620577</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2096899</t>
+          <t>2128974</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1718808</t>
+          <t>1710089</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2205234</t>
+          <t>2250703</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3401108</t>
+          <t>3409289</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4104848</t>
+          <t>4107840</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD14_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD14_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>55881</t>
+          <t>70031</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>53590</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70459</t>
+          <t>87882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>77089</t>
+          <t>84576</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65927</t>
+          <t>71953</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88410</t>
+          <t>97931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>132970</t>
+          <t>154608</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116934</t>
+          <t>135245</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>149822</t>
+          <t>177535</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>234674</t>
+          <t>260378</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>213185</t>
+          <t>238627</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>254969</t>
+          <t>282819</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,22 +873,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>383109</t>
+          <t>416816</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>363092</t>
+          <t>395070</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>406359</t>
+          <t>440630</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>617783</t>
+          <t>677194</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>587029</t>
+          <t>642944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>646760</t>
+          <t>710379</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,98%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>219657</t>
+          <t>243120</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199938</t>
+          <t>222095</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>242573</t>
+          <t>265122</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>293222</t>
+          <t>318491</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>271768</t>
+          <t>295236</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313547</t>
+          <t>339592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>512879</t>
+          <t>561611</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>484750</t>
+          <t>530519</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>542875</t>
+          <t>593366</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,58%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>510212</t>
+          <t>573529</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>510212</t>
+          <t>573529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>510212</t>
+          <t>573529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>753420</t>
+          <t>819884</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>753420</t>
+          <t>819884</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>753420</t>
+          <t>819884</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1263632</t>
+          <t>1393413</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1263632</t>
+          <t>1393413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1263632</t>
+          <t>1393413</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>174084</t>
+          <t>198957</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116024</t>
+          <t>167264</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>213276</t>
+          <t>234318</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>183765</t>
+          <t>211917</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>134813</t>
+          <t>186047</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>218374</t>
+          <t>239720</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>357849</t>
+          <t>410874</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>279290</t>
+          <t>371189</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>410558</t>
+          <t>452937</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>889004</t>
+          <t>973620</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>618243</t>
+          <t>915877</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1017365</t>
+          <t>1023334</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>846102</t>
+          <t>912700</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>588762</t>
+          <t>866446</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>969756</t>
+          <t>955508</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1735106</t>
+          <t>1886320</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1416083</t>
+          <t>1820435</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1938716</t>
+          <t>1956494</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>44,65%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1221523</t>
+          <t>1050585</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1076106</t>
+          <t>999011</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1567324</t>
+          <t>1105225</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1197146</t>
+          <t>1034543</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1052518</t>
+          <t>993108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1510838</t>
+          <t>1079407</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2418668</t>
+          <t>2085128</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2176152</t>
+          <t>2014650</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2802956</t>
+          <t>2153573</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>49,14%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2284611</t>
+          <t>2223162</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2284611</t>
+          <t>2223162</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2284611</t>
+          <t>2223162</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2227012</t>
+          <t>2159160</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2227012</t>
+          <t>2159160</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2227012</t>
+          <t>2159160</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4511623</t>
+          <t>4382322</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4511623</t>
+          <t>4382322</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4511623</t>
+          <t>4382322</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60029</t>
+          <t>61048</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43455</t>
+          <t>46125</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89220</t>
+          <t>80496</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>72238</t>
+          <t>82156</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59076</t>
+          <t>67136</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86303</t>
+          <t>98487</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>132267</t>
+          <t>143204</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>110661</t>
+          <t>120980</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>162131</t>
+          <t>167009</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>250209</t>
+          <t>281635</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>221988</t>
+          <t>256438</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>277916</t>
+          <t>310702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>223301</t>
+          <t>256193</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>203228</t>
+          <t>233522</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>247904</t>
+          <t>281282</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>473510</t>
+          <t>537828</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>438415</t>
+          <t>500520</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>511078</t>
+          <t>575413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>334474</t>
+          <t>367092</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>305939</t>
+          <t>338545</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365064</t>
+          <t>395098</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>364924</t>
+          <t>396527</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>341960</t>
+          <t>371989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386989</t>
+          <t>423067</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>699399</t>
+          <t>763619</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>659762</t>
+          <t>725236</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>736355</t>
+          <t>803059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>55,59%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>644712</t>
+          <t>709775</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>644712</t>
+          <t>709775</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>644712</t>
+          <t>709775</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1305175</t>
+          <t>1444652</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1305175</t>
+          <t>1444652</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1305175</t>
+          <t>1444652</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>289994</t>
+          <t>330036</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>228834</t>
+          <t>291095</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>336842</t>
+          <t>371822</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,67 +2128,67 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>333092</t>
+          <t>378650</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>274702</t>
+          <t>348538</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>372062</t>
+          <t>412295</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>708686</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>660930</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>768014</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>9,82%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>9,15%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>10,22%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>805</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>623086</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>537739</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>689951</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>7,59%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1373886</t>
+          <t>1515633</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1086852</t>
+          <t>1448360</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1507509</t>
+          <t>1579485</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1452511</t>
+          <t>1585709</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1144012</t>
+          <t>1535361</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1579608</t>
+          <t>1645836</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2826398</t>
+          <t>3101342</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2456077</t>
+          <t>3008580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3008180</t>
+          <t>3179012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1775654</t>
+          <t>1660797</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1620577</t>
+          <t>1597899</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2128974</t>
+          <t>1725743</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1855292</t>
+          <t>1749562</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1710089</t>
+          <t>1693207</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2250703</t>
+          <t>1800936</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3630946</t>
+          <t>3410358</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3409289</t>
+          <t>3328490</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4107840</t>
+          <t>3496039</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>48,42%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3439535</t>
+          <t>3506466</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3439535</t>
+          <t>3506466</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3439535</t>
+          <t>3506466</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3640895</t>
+          <t>3713921</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3640895</t>
+          <t>3713921</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3640895</t>
+          <t>3713921</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7080430</t>
+          <t>7220387</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7080430</t>
+          <t>7220387</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7080430</t>
+          <t>7220387</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
